--- a/benchmarks/CATBOOST_V3_FORECASTING/catboost_results.xlsx
+++ b/benchmarks/CATBOOST_V3_FORECASTING/catboost_results.xlsx
@@ -473,13 +473,13 @@
         <v>2021</v>
       </c>
       <c r="D2" t="n">
-        <v>5.959406957106399</v>
+        <v>5.950139514285244</v>
       </c>
       <c r="E2" t="n">
-        <v>24.32209112516535</v>
+        <v>24.66980029504966</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7438330566224529</v>
+        <v>0.7405359528652102</v>
       </c>
     </row>
     <row r="3">
@@ -493,13 +493,13 @@
         <v>2022</v>
       </c>
       <c r="D3" t="n">
-        <v>14.19115102343225</v>
+        <v>14.43284484800452</v>
       </c>
       <c r="E3" t="n">
-        <v>56.14028520532404</v>
+        <v>56.77994950253341</v>
       </c>
       <c r="F3" t="n">
-        <v>0.775286125332407</v>
+        <v>0.776414564873108</v>
       </c>
     </row>
     <row r="4">
@@ -513,13 +513,13 @@
         <v>2023</v>
       </c>
       <c r="D4" t="n">
-        <v>16.38894808323462</v>
+        <v>14.4362038773686</v>
       </c>
       <c r="E4" t="n">
-        <v>63.67503668468792</v>
+        <v>55.03399282189306</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7294799149508654</v>
+        <v>0.7891632407357756</v>
       </c>
     </row>
     <row r="5">
@@ -533,13 +533,13 @@
         <v>2024</v>
       </c>
       <c r="D5" t="n">
-        <v>35.21244285870497</v>
+        <v>33.41478347590108</v>
       </c>
       <c r="E5" t="n">
-        <v>111.141789698822</v>
+        <v>107.5021558846122</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8206207968225557</v>
+        <v>0.8369959907370579</v>
       </c>
     </row>
     <row r="6">
@@ -553,13 +553,13 @@
         <v>2025</v>
       </c>
       <c r="D6" t="n">
-        <v>17.00250024422308</v>
+        <v>14.91291065158947</v>
       </c>
       <c r="E6" t="n">
-        <v>45.93096658514945</v>
+        <v>43.657407981708</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8408798521450237</v>
+        <v>0.8562427029864411</v>
       </c>
     </row>
   </sheetData>
@@ -600,10 +600,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>17.75088983334027</v>
+        <v>16.62937647342978</v>
       </c>
       <c r="C2" t="n">
-        <v>10.71251155402743</v>
+        <v>10.10416996100279</v>
       </c>
     </row>
     <row r="3">
@@ -613,10 +613,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>60.24203385982976</v>
+        <v>57.52866129715927</v>
       </c>
       <c r="C3" t="n">
-        <v>32.07196566898905</v>
+        <v>30.72560217608627</v>
       </c>
     </row>
     <row r="4">
@@ -626,10 +626,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7820199491746609</v>
+        <v>0.7998704904395185</v>
       </c>
       <c r="C4" t="n">
-        <v>0.04800664526757337</v>
+        <v>0.04674810720588136</v>
       </c>
     </row>
   </sheetData>
@@ -643,7 +643,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B69"/>
+  <dimension ref="A1:B67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>52.09291125010244</v>
+        <v>52.05900914740289</v>
       </c>
     </row>
     <row r="3">
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>29.67180585486292</v>
+        <v>26.83574669227085</v>
       </c>
     </row>
     <row r="4">
@@ -685,7 +685,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9.253124738596487</v>
+        <v>11.65746187635987</v>
       </c>
     </row>
     <row r="5">
@@ -695,7 +695,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.998071470249653</v>
+        <v>2.553844907007524</v>
       </c>
     </row>
     <row r="6">
@@ -705,67 +705,67 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.24975610614963</v>
+        <v>1.95164202402161</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>semana</t>
+          <t>Rt_lag_2</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9012927391605861</v>
+        <v>1.100265474728111</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Rt_lag_2</t>
+          <t>mes</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6269341052588344</v>
+        <v>1.008899319733968</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>anio</t>
+          <t>Rt_lag_1</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5119949940131515</v>
+        <v>0.5109011886569725</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>mes</t>
+          <t>pct_cropland</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.3699480289555125</v>
+        <v>0.2353791360762497</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Rt_lag_1</t>
+          <t>Rt_lag_4</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2735234633256136</v>
+        <v>0.2330968201353965</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Rt_lag_4</t>
+          <t>nino34</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.2696988626435582</v>
+        <v>0.1874873187390543</v>
       </c>
     </row>
     <row r="13">
@@ -775,97 +775,97 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2380194208721606</v>
+        <v>0.1848870775316435</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>nino34</t>
+          <t>EVI_mean</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1802628413911692</v>
+        <v>0.1367305335075919</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>pct_cropland</t>
+          <t>tempmed_lag_1</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1675365824071072</v>
+        <v>0.1331978180901887</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>casos_lag_8</t>
+          <t>soi</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1227151253640807</v>
+        <v>0.1193323942097939</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>precip_roll4_sum</t>
+          <t>precip_roll8_sum</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.06892482480475463</v>
+        <v>0.08776754576725102</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>LST_Night_mean</t>
+          <t>casos_lag_8</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.06766392520939353</v>
+        <v>0.077405211669094</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>pct_wetland</t>
+          <t>LST_Night_mean</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.05974597618095762</v>
+        <v>0.07352116073021553</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>soi</t>
+          <t>LST_Day_mean</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.04736440268164321</v>
+        <v>0.06805748245638915</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>precip_total_semana_lag_1</t>
+          <t>pct_shrubland</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.04366000284921508</v>
+        <v>0.06656542094350322</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>pct_bare_sparse</t>
+          <t>precip_roll4_sum</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.04286944762969317</v>
+        <v>0.05852615171641525</v>
       </c>
     </row>
     <row r="23">
@@ -875,47 +875,47 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.04241055665625802</v>
+        <v>0.04976859669024704</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>precip_roll8_sum</t>
+          <t>precip_total_semana_lag_4</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.03633429013819687</v>
+        <v>0.04857857629297365</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>umidmax</t>
+          <t>aging_index</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.03610469202129696</v>
+        <v>0.03950039916226818</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>precip_total_semana_lag_4</t>
+          <t>NDVI_mean</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.0306719311838323</v>
+        <v>0.03665453052932903</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>water_supply_pct</t>
+          <t>pct_wetland</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.02989431843490497</v>
+        <v>0.03471380330950678</v>
       </c>
     </row>
     <row r="28">
@@ -925,157 +925,157 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.02938357455567328</v>
+        <v>0.03371908934561136</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>LST_Day_mean</t>
+          <t>tempmed_lag_4</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.02905764512824678</v>
+        <v>0.03192282071014806</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>tempmed_roll4_mean</t>
+          <t>area_km2</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.02710926881035149</v>
+        <v>0.03122133186899887</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>area_km2</t>
+          <t>NDVI_std</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.02661889195311922</v>
+        <v>0.03037809632693093</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>tempmed_lag_1</t>
+          <t>casos_lag_4</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.02566048507469196</v>
+        <v>0.02678416588110531</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>tempmax</t>
+          <t>tempmed</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.02392662105378424</v>
+        <v>0.02044271481559676</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>male_population_pct</t>
+          <t>tempmed_roll4_mean</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.02284889956933897</v>
+        <v>0.01867653876825847</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>tempmed</t>
+          <t>sex_ratio</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.02209287393050087</v>
+        <v>0.01521323037780745</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>NDVI_mean</t>
+          <t>pct_grassland</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.02146858466861606</v>
+        <v>0.01455448013915649</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>sex_ratio</t>
+          <t>umidmed_lag_4</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.01955407031691425</v>
+        <v>0.01406767947180187</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>EVI_mean</t>
+          <t>male_population_pct</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.01939829917394824</v>
+        <v>0.01397527006156301</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>casos_lag_4</t>
+          <t>water_supply_pct</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.01784144919594872</v>
+        <v>0.01384773142770467</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>pct_tree_cover</t>
+          <t>precip_total_semana_lag_1</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.01700306949496943</v>
+        <v>0.01098696506053997</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>precip_total_semana</t>
+          <t>elev_mean</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.01492075032727203</v>
+        <v>0.01095688014490915</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>female_population_pct</t>
+          <t>tempmax</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.01482506786961307</v>
+        <v>0.01078485165517332</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>umidmed_lag_4</t>
+          <t>sewage_pct</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.01425068075993853</v>
+        <v>0.01072467104203966</v>
       </c>
     </row>
     <row r="44">
@@ -1085,37 +1085,37 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.01311790224534006</v>
+        <v>0.01046898558979347</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>pct_builtup</t>
+          <t>EVI_std</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.01292134589896744</v>
+        <v>0.01041562455878967</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>precip_max_semana</t>
+          <t>female_population_pct</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.01274870379402664</v>
+        <v>0.01034575898848787</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>NDVI_std</t>
+          <t>n_pixels</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.01270998174727105</v>
+        <v>0.01003548549325747</v>
       </c>
     </row>
     <row r="48">
@@ -1125,17 +1125,17 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.01260342088602177</v>
+        <v>0.009717535323897745</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>elev_mean</t>
+          <t>tempmed_roll8_mean</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.01228151849084152</v>
+        <v>0.009371205752910651</v>
       </c>
     </row>
     <row r="50">
@@ -1145,196 +1145,176 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.0109672211834011</v>
+        <v>0.009357234244278166</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>n_pixels</t>
+          <t>LST_Night_std</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.010906582735044</v>
+        <v>0.008228784897794205</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>umidmed_lag_1</t>
+          <t>umidmax</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.0102528624548104</v>
+        <v>0.007716604037688542</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>tempmed_roll8_mean</t>
+          <t>population_density</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.01018159977504366</v>
+        <v>0.007677256064960424</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>umidmin</t>
+          <t>garbage_collection_pct</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.01016526042832385</v>
+        <v>0.006904644291258563</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>pct_shrubland</t>
+          <t>pct_bare_sparse</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.01012769880507216</v>
+        <v>0.006816606793084384</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>tempmed_lag_4</t>
+          <t>precip_total_semana</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.009942446702298241</v>
+        <v>0.005920585308382848</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>aging_index</t>
+          <t>umidmed</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.009869044251477551</v>
+        <v>0.005253023464153402</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>umidmed</t>
+          <t>pct_builtup</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.00951307178814359</v>
+        <v>0.00516625785180882</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>sewage_pct</t>
+          <t>LST_Day_std</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.009130560387698869</v>
+        <v>0.004909326304190232</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>LST_Day_std</t>
+          <t>precip_max_semana</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.007601942525393542</v>
+        <v>0.004799663183484714</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>EVI_std</t>
+          <t>pct_tree_cover</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.007599632267746717</v>
+        <v>0.003917163386731424</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>dias_lluvia_semana</t>
+          <t>elev_min</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.00664577673258981</v>
+        <v>0.002707758795540719</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>population_density</t>
+          <t>umidmin</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.006175444724957388</v>
+        <v>0.001516720151490193</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>pct_grassland</t>
+          <t>umidmed_lag_1</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.005829019745901581</v>
+        <v>0.0007871606330262529</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>elev_min</t>
+          <t>n_tiles</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.004843206080274874</v>
+        <v>0.0005905532886702395</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>garbage_collection_pct</t>
+          <t>pct_mangroves</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.003855984626918228</v>
+        <v>0.0001789367600889436</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>LST_Night_std</t>
+          <t>dias_lluvia_semana</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.0008095886964288623</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>n_tiles</t>
-        </is>
-      </c>
-      <c r="B68" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>pct_mangroves</t>
-        </is>
-      </c>
-      <c r="B69" t="n">
         <v>0</v>
       </c>
     </row>
